--- a/作業票.xlsx
+++ b/作業票.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\3DRPG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77BAF82-543D-4775-B03A-643FEF169815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80ABC1F3-3189-4FED-8F49-600E0B78824F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{41B48087-E4EE-4E9E-AF83-941FF13AEAD0}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$E$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$F$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="24">
   <si>
     <t>タスク</t>
     <phoneticPr fontId="1"/>
@@ -67,80 +67,6 @@
     <t>番号</t>
     <rPh sb="0" eb="2">
       <t>バンゴウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プルダウン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作業中（うじいえ）</t>
-    <rPh sb="0" eb="3">
-      <t>サギョウチュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作業中（けんご）</t>
-    <rPh sb="0" eb="3">
-      <t>サギョウチュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作業中（いわぶち）</t>
-    <rPh sb="0" eb="3">
-      <t>サギョウチュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作業中（ほうしょう）</t>
-    <rPh sb="0" eb="3">
-      <t>サギョウチュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作業中（くめた）</t>
-    <rPh sb="0" eb="3">
-      <t>サギョウチュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作業完了（うじいえ）</t>
-    <rPh sb="0" eb="4">
-      <t>サギョウカンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作業完了（けんご）</t>
-    <rPh sb="0" eb="4">
-      <t>サギョウカンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作業完了（いわぶち）</t>
-    <rPh sb="0" eb="4">
-      <t>サギョウカンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作業完了（ほうしょう）</t>
-    <rPh sb="0" eb="4">
-      <t>サギョウカンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作業完了（くめた）</t>
-    <rPh sb="0" eb="4">
-      <t>サギョウカンリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -232,6 +158,86 @@
     <t>ダメージ計算</t>
     <rPh sb="4" eb="6">
       <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作業中</t>
+    <rPh sb="0" eb="3">
+      <t>サギョウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作業完了</t>
+    <rPh sb="0" eb="4">
+      <t>サギョウカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>担当</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>進捗</t>
+    <rPh sb="0" eb="2">
+      <t>シンチョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いわぶち</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>けんご</t>
+  </si>
+  <si>
+    <t>けんご</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>うじいえ</t>
+  </si>
+  <si>
+    <t>うじいえ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ほうしょう</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>くめた</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>担当</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>運、相性倍率（表示問題）のデータ形式は要相談。</t>
+    <rPh sb="0" eb="1">
+      <t>ウン</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>アイショウバイリツ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ヒョウジモンダイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>ヨウソウダン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -271,7 +277,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -434,13 +440,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -482,37 +529,28 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAF2D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -527,76 +565,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFDAF2D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -944,276 +912,317 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41F50AC-64FE-4975-A154-19305FADBFE4}">
-  <dimension ref="B1:E23"/>
+  <dimension ref="B1:F23"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="1.8125" customWidth="1"/>
     <col min="2" max="2" width="8.8125" customWidth="1"/>
     <col min="3" max="3" width="54.25" customWidth="1"/>
-    <col min="4" max="4" width="18.25" customWidth="1"/>
-    <col min="5" max="5" width="54.25" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="18.25" customWidth="1"/>
+    <col min="6" max="6" width="54.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="7.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.75"/>
-    <row r="2" spans="2:5" ht="18" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="2:6" ht="7.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.75"/>
+    <row r="2" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.75">
       <c r="B2" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="52.9" x14ac:dyDescent="0.7">
+    <row r="3" spans="2:6" ht="52.9" x14ac:dyDescent="0.7">
       <c r="B3" s="8">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="F3" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B4" s="8">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B5" s="8">
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.7">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B6" s="8">
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.7">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B7" s="8">
         <v>5</v>
       </c>
       <c r="C7" s="4"/>
-      <c r="D7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D7" s="3"/>
+      <c r="E7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B8" s="8">
         <v>6</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D8" s="3"/>
+      <c r="E8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B9" s="8">
         <v>7</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D9" s="3"/>
+      <c r="E9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B10" s="8">
         <v>8</v>
       </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D10" s="3"/>
+      <c r="E10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B11" s="8">
         <v>9</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D11" s="3"/>
+      <c r="E11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B12" s="8">
         <v>10</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D12" s="3"/>
+      <c r="E12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B13" s="8">
         <v>11</v>
       </c>
       <c r="C13" s="4"/>
-      <c r="D13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D13" s="3"/>
+      <c r="E13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B14" s="8">
         <v>12</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D14" s="3"/>
+      <c r="E14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B15" s="8">
         <v>13</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D15" s="3"/>
+      <c r="E15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B16" s="8">
         <v>14</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D16" s="3"/>
+      <c r="E16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B17" s="8">
         <v>15</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D17" s="3"/>
+      <c r="E17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B18" s="8">
         <v>16</v>
       </c>
       <c r="C18" s="4"/>
-      <c r="D18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D18" s="3"/>
+      <c r="E18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B19" s="8">
         <v>17</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D19" s="3"/>
+      <c r="E19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B20" s="8">
         <v>18</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D20" s="3"/>
+      <c r="E20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B21" s="8">
         <v>19</v>
       </c>
       <c r="C21" s="4"/>
-      <c r="D21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D21" s="3"/>
+      <c r="E21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B22" s="8">
         <v>20</v>
       </c>
       <c r="C22" s="4"/>
-      <c r="D22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D22" s="3"/>
+      <c r="E22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B23" s="8">
         <v>21</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="2"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:E23" xr:uid="{B41F50AC-64FE-4975-A154-19305FADBFE4}"/>
+  <autoFilter ref="B2:F23" xr:uid="{B41F50AC-64FE-4975-A154-19305FADBFE4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="D1:D1048576">
+  <conditionalFormatting sqref="E1:E1048576">
     <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="作業完了">
-      <formula>NOT(ISERROR(SEARCH("作業完了",D1)))</formula>
+      <formula>NOT(ISERROR(SEARCH("作業完了",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="作業中">
-      <formula>NOT(ISERROR(SEARCH("作業中",D1)))</formula>
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="作業中">
+      <formula>NOT(ISERROR(SEARCH("作業中",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="未達成">
-      <formula>NOT(ISERROR(SEARCH("未達成",D1)))</formula>
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="未達成">
+      <formula>NOT(ISERROR(SEARCH("未達成",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6D66443B-96C7-49CA-968A-9BFD64943CEF}">
           <x14:formula1>
-            <xm:f>Sheet2!$B$2:$B$12</xm:f>
+            <xm:f>Sheet2!$C$2:$C$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D1:D1048576</xm:sqref>
+          <xm:sqref>E1:E1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C37E05EE-FB64-46F8-B962-042D2DB124A7}">
+          <x14:formula1>
+            <xm:f>Sheet2!$B$2:$B$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3:D1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1223,77 +1232,59 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C5A889F-C21C-4947-854F-499394BFB61D}">
-  <dimension ref="B1:B12"/>
+  <dimension ref="B1:C6"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="2" max="2" width="22.75" customWidth="1"/>
+    <col min="3" max="3" width="22.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" ht="18" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.75">
       <c r="B1" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.7">
+        <v>13</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.7">
       <c r="B2" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.7">
+        <v>15</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.7">
       <c r="B3" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.7">
-      <c r="B4" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.7">
-      <c r="B5" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.7">
-      <c r="B6" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.7">
-      <c r="B7" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.7">
-      <c r="B8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.7">
-      <c r="B9" s="11" t="s">
+    <row r="4" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="B4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.7">
-      <c r="B10" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.7">
-      <c r="B11" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" ht="18" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="B12" s="12" t="s">
-        <v>15</v>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.7">
+      <c r="B5" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="B6" s="16" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="C1">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="未達成">
-      <formula>NOT(ISERROR(SEARCH("未達成",C1)))</formula>
+  <conditionalFormatting sqref="D1">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="未達成">
+      <formula>NOT(ISERROR(SEARCH("未達成",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
